--- a/database/mau_nhap_so_dien_nuoc.xlsx
+++ b/database/mau_nhap_so_dien_nuoc.xlsx
@@ -404,10 +404,10 @@
         <v>Ma can ho</v>
       </c>
       <c r="B1" t="str">
-        <v>Chi so dien thang</v>
+        <v>Chi so dien thang 7</v>
       </c>
       <c r="C1" t="str">
-        <v>Chi so nuoc thang</v>
+        <v>Chi so nuoc thang 7</v>
       </c>
     </row>
     <row r="2">
@@ -415,10 +415,10 @@
         <v>A-101</v>
       </c>
       <c r="B2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -426,10 +426,10 @@
         <v>A-102</v>
       </c>
       <c r="B3">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -440,7 +440,7 @@
         <v>280</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -448,10 +448,10 @@
         <v>A-302</v>
       </c>
       <c r="B5">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -459,10 +459,10 @@
         <v>B-101</v>
       </c>
       <c r="B6">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -470,10 +470,10 @@
         <v>B-102</v>
       </c>
       <c r="B7">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -481,10 +481,10 @@
         <v>B-201</v>
       </c>
       <c r="B8">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C8">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -492,10 +492,10 @@
         <v>B-302</v>
       </c>
       <c r="B9">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
